--- a/sheets/대금율보/검수/성주푸리.xlsx
+++ b/sheets/대금율보/검수/성주푸리.xlsx
@@ -12051,32 +12051,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="119.22" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="119.22" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="119.22" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="23"/>
@@ -12334,7 +12334,7 @@
       <c r="T5" s="21"/>
       <c r="U5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="119.22" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="119.22" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
       <c r="T7" s="21"/>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="119.22" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="23"/>
@@ -12522,7 +12522,7 @@
       <c r="T8" s="21"/>
       <c r="U8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="119.22" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="119.22" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="24"/>
@@ -12701,7 +12701,7 @@
       <c r="T10" s="21"/>
       <c r="U10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="119.22" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
       <c r="T11" s="21"/>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="119.22" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
@@ -12804,7 +12804,7 @@
       <c r="T12" s="21"/>
       <c r="U12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="119.22" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -12851,7 +12851,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="119.22" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -12922,10 +12922,10 @@
       </c>
       <c r="U14" s="24"/>
     </row>
-    <row r="15">
+    <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="80.0" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="119.22" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="119.22" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
       <c r="T18" s="21"/>
       <c r="U18" s="23"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="119.22" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="119.22" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
       <c r="T20" s="21"/>
       <c r="U20" s="24"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="119.22" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="119.22" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
       <c r="T22" s="21"/>
       <c r="U22" s="23"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="119.22" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="119.22" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
       <c r="T24" s="21"/>
       <c r="U24" s="24"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="119.22" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="22"/>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="U25" s="22"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="119.22" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
       </c>
       <c r="U26" s="23"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="119.22" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="U27" s="23"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="119.22" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21" t="inlineStr">
         <is>
@@ -13976,10 +13976,10 @@
       </c>
       <c r="U28" s="24"/>
     </row>
-    <row r="29">
+    <row r="29" ht="6.0" customHeight="true">
       <c r="A29" s="0"/>
     </row>
-    <row r="30" ht="60" customHeight="1">
+    <row r="30" ht="80.0" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="20" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
       <c r="T30" s="20"/>
       <c r="U30" s="20"/>
     </row>
-    <row r="31" ht="56" customHeight="1">
+    <row r="31" ht="119.22" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="56" customHeight="1">
+    <row r="32" ht="119.22" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="119.22" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="119.22" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="56" customHeight="1">
+    <row r="35" ht="119.22" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="56" customHeight="1">
+    <row r="36" ht="119.22" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="56" customHeight="1">
+    <row r="37" ht="119.22" customHeight="true">
       <c r="A37" s="0"/>
       <c r="B37" s="21" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="56" customHeight="1">
+    <row r="38" ht="119.22" customHeight="true">
       <c r="A38" s="0"/>
       <c r="B38" s="21" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="56" customHeight="1">
+    <row r="39" ht="119.22" customHeight="true">
       <c r="A39" s="0"/>
       <c r="B39" s="21" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="56" customHeight="1">
+    <row r="40" ht="119.22" customHeight="true">
       <c r="A40" s="0"/>
       <c r="B40" s="21" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="56" customHeight="1">
+    <row r="41" ht="119.22" customHeight="true">
       <c r="A41" s="0"/>
       <c r="B41" s="21" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="56" customHeight="1">
+    <row r="42" ht="119.22" customHeight="true">
       <c r="A42" s="0"/>
       <c r="B42" s="21" t="inlineStr">
         <is>
@@ -15027,10 +15027,10 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="6.0" customHeight="true">
       <c r="A43" s="0"/>
     </row>
-    <row r="44" ht="60" customHeight="1">
+    <row r="44" ht="80.0" customHeight="true">
       <c r="A44" s="0"/>
       <c r="B44" s="20" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
       <c r="T44" s="20"/>
       <c r="U44" s="20"/>
     </row>
-    <row r="45" ht="56" customHeight="1">
+    <row r="45" ht="119.22" customHeight="true">
       <c r="A45" s="0"/>
       <c r="B45" s="21"/>
       <c r="C45" s="22"/>
@@ -15100,7 +15100,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="56" customHeight="1">
+    <row r="46" ht="119.22" customHeight="true">
       <c r="A46" s="0"/>
       <c r="B46" s="21"/>
       <c r="C46" s="23"/>
@@ -15135,7 +15135,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="56" customHeight="1">
+    <row r="47" ht="119.22" customHeight="true">
       <c r="A47" s="0"/>
       <c r="B47" s="21"/>
       <c r="C47" s="23"/>
@@ -15162,7 +15162,7 @@
       <c r="T47" s="21"/>
       <c r="U47" s="23"/>
     </row>
-    <row r="48" ht="56" customHeight="1">
+    <row r="48" ht="119.22" customHeight="true">
       <c r="A48" s="0"/>
       <c r="B48" s="21"/>
       <c r="C48" s="24"/>
@@ -15197,7 +15197,7 @@
       </c>
       <c r="U48" s="24"/>
     </row>
-    <row r="49" ht="56" customHeight="1">
+    <row r="49" ht="119.22" customHeight="true">
       <c r="A49" s="0"/>
       <c r="B49" s="21"/>
       <c r="C49" s="22"/>
@@ -15229,7 +15229,7 @@
       <c r="T49" s="21"/>
       <c r="U49" s="22"/>
     </row>
-    <row r="50" ht="56" customHeight="1">
+    <row r="50" ht="119.22" customHeight="true">
       <c r="A50" s="0"/>
       <c r="B50" s="21"/>
       <c r="C50" s="23"/>
@@ -15260,7 +15260,7 @@
       <c r="T50" s="21"/>
       <c r="U50" s="23"/>
     </row>
-    <row r="51" ht="56" customHeight="1">
+    <row r="51" ht="119.22" customHeight="true">
       <c r="A51" s="0"/>
       <c r="B51" s="21"/>
       <c r="C51" s="23"/>
@@ -15303,7 +15303,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="56" customHeight="1">
+    <row r="52" ht="119.22" customHeight="true">
       <c r="A52" s="0"/>
       <c r="B52" s="21"/>
       <c r="C52" s="24"/>
@@ -15347,7 +15347,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="56" customHeight="1">
+    <row r="53" ht="119.22" customHeight="true">
       <c r="A53" s="0"/>
       <c r="B53" s="21"/>
       <c r="C53" s="22"/>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="U53" s="22"/>
     </row>
-    <row r="54" ht="56" customHeight="1">
+    <row r="54" ht="119.22" customHeight="true">
       <c r="A54" s="0"/>
       <c r="B54" s="21"/>
       <c r="C54" s="23"/>
@@ -15418,7 +15418,7 @@
       </c>
       <c r="U54" s="23"/>
     </row>
-    <row r="55" ht="56" customHeight="1">
+    <row r="55" ht="119.22" customHeight="true">
       <c r="A55" s="0"/>
       <c r="B55" s="21"/>
       <c r="C55" s="23"/>
@@ -15453,7 +15453,7 @@
       </c>
       <c r="U55" s="23"/>
     </row>
-    <row r="56" ht="56" customHeight="1">
+    <row r="56" ht="119.22" customHeight="true">
       <c r="A56" s="0"/>
       <c r="B56" s="21"/>
       <c r="C56" s="24"/>
@@ -15495,7 +15495,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="14" max="16383" man="1"/>
     <brk id="28" max="16383" man="1"/>
